--- a/Hyderabad-June-2025.xlsx
+++ b/Hyderabad-June-2025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="130" uniqueCount="61">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="136" uniqueCount="71">
   <si>
     <t>Sr. No</t>
   </si>
@@ -94,6 +94,9 @@
     <t>Profit %</t>
   </si>
   <si>
+    <t>Unnamed: 26</t>
+  </si>
+  <si>
     <t>Hyderabad</t>
   </si>
   <si>
@@ -148,13 +151,13 @@
     <t>MH43BP4027</t>
   </si>
   <si>
-    <t>TS09UE 3183</t>
-  </si>
-  <si>
-    <t>TS09UE 3184</t>
-  </si>
-  <si>
-    <t>TS09UE 3198</t>
+    <t>TS09UE3183</t>
+  </si>
+  <si>
+    <t>TS09UE3184</t>
+  </si>
+  <si>
+    <t>TS09UE3198</t>
   </si>
   <si>
     <t>TS09UE3947</t>
@@ -175,34 +178,64 @@
     <t>JAGUAR</t>
   </si>
   <si>
-    <t>Crysta</t>
+    <t>CRYSTA</t>
   </si>
   <si>
     <t>CAMRY</t>
   </si>
   <si>
-    <t>Etios</t>
-  </si>
-  <si>
-    <t>Bolero</t>
-  </si>
-  <si>
-    <t>Safari</t>
-  </si>
-  <si>
-    <t>BYD</t>
-  </si>
-  <si>
-    <t>Dzire</t>
-  </si>
-  <si>
-    <t>-</t>
+    <t>ETIOS</t>
+  </si>
+  <si>
+    <t>BOLERO</t>
+  </si>
+  <si>
+    <t>SAFARI</t>
+  </si>
+  <si>
+    <t>BYD E6</t>
+  </si>
+  <si>
+    <t>DZIRE</t>
+  </si>
+  <si>
+    <t>29/09/2018</t>
+  </si>
+  <si>
+    <t>14/08/2018</t>
+  </si>
+  <si>
+    <t>18/02/2020</t>
+  </si>
+  <si>
+    <t>19/12/2019</t>
+  </si>
+  <si>
+    <t>31/10/2023</t>
+  </si>
+  <si>
+    <t>26/12/2019</t>
+  </si>
+  <si>
+    <t>31/05/2022</t>
+  </si>
+  <si>
+    <t>30/03/2019</t>
+  </si>
+  <si>
+    <t>17/07/2019</t>
+  </si>
+  <si>
+    <t>14/03/2024</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="YYYY-MM-DD HH:MM:SS"/>
+  </numFmts>
   <fonts count="2">
     <font>
       <sz val="11"/>
@@ -255,11 +288,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -554,10 +588,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Z25"/>
+  <dimension ref="A1:AA25"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:26">
+    <row r="1" spans="1:27">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -636,28 +670,31 @@
       <c r="Z1" s="1" t="s">
         <v>25</v>
       </c>
+      <c r="AA1" s="1" t="s">
+        <v>26</v>
+      </c>
     </row>
-    <row r="2" spans="1:26">
+    <row r="2" spans="1:27">
       <c r="A2">
         <v>90</v>
       </c>
       <c r="B2" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C2" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D2">
         <v>2025</v>
       </c>
       <c r="E2" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="F2" t="s">
-        <v>52</v>
-      </c>
-      <c r="G2">
-        <v>43372</v>
+        <v>53</v>
+      </c>
+      <c r="G2" t="s">
+        <v>61</v>
       </c>
       <c r="H2">
         <v>130918</v>
@@ -717,27 +754,27 @@
         <v>78.3</v>
       </c>
     </row>
-    <row r="3" spans="1:26">
+    <row r="3" spans="1:27">
       <c r="A3">
         <v>91</v>
       </c>
       <c r="B3" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C3" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D3">
         <v>2025</v>
       </c>
       <c r="E3" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="F3" t="s">
-        <v>53</v>
-      </c>
-      <c r="G3">
-        <v>43326</v>
+        <v>54</v>
+      </c>
+      <c r="G3" t="s">
+        <v>62</v>
       </c>
       <c r="H3">
         <v>157140</v>
@@ -797,27 +834,27 @@
         <v>58.9</v>
       </c>
     </row>
-    <row r="4" spans="1:26">
+    <row r="4" spans="1:27">
       <c r="A4">
         <v>92</v>
       </c>
       <c r="B4" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C4" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D4">
         <v>2025</v>
       </c>
       <c r="E4" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="F4" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="G4" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="H4">
         <v>158664</v>
@@ -877,27 +914,27 @@
         <v>-64.16</v>
       </c>
     </row>
-    <row r="5" spans="1:26">
+    <row r="5" spans="1:27">
       <c r="A5">
         <v>93</v>
       </c>
       <c r="B5" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C5" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D5">
         <v>2025</v>
       </c>
       <c r="E5" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F5" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="G5" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="H5">
         <v>175774</v>
@@ -957,27 +994,27 @@
         <v>50.92</v>
       </c>
     </row>
-    <row r="6" spans="1:26">
+    <row r="6" spans="1:27">
       <c r="A6">
         <v>94</v>
       </c>
       <c r="B6" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C6" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D6">
         <v>2025</v>
       </c>
       <c r="E6" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F6" t="s">
-        <v>53</v>
-      </c>
-      <c r="G6">
-        <v>43879</v>
+        <v>54</v>
+      </c>
+      <c r="G6" t="s">
+        <v>63</v>
       </c>
       <c r="H6">
         <v>112520</v>
@@ -1037,27 +1074,27 @@
         <v>53.42</v>
       </c>
     </row>
-    <row r="7" spans="1:26">
+    <row r="7" spans="1:27">
       <c r="A7">
         <v>95</v>
       </c>
       <c r="B7" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C7" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D7">
         <v>2025</v>
       </c>
       <c r="E7" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="F7" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="G7" t="s">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="H7">
         <v>313040</v>
@@ -1117,27 +1154,27 @@
         <v>50.5</v>
       </c>
     </row>
-    <row r="8" spans="1:26">
+    <row r="8" spans="1:27">
       <c r="A8">
         <v>96</v>
       </c>
       <c r="B8" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C8" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D8">
         <v>2025</v>
       </c>
       <c r="E8" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="F8" t="s">
-        <v>53</v>
-      </c>
-      <c r="G8" t="s">
-        <v>60</v>
+        <v>54</v>
+      </c>
+      <c r="G8" s="2">
+        <v>43283</v>
       </c>
       <c r="H8">
         <v>232705</v>
@@ -1197,27 +1234,27 @@
         <v>63.19</v>
       </c>
     </row>
-    <row r="9" spans="1:26">
+    <row r="9" spans="1:27">
       <c r="A9">
         <v>97</v>
       </c>
       <c r="B9" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C9" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D9">
         <v>2025</v>
       </c>
       <c r="E9" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="F9" t="s">
-        <v>53</v>
-      </c>
-      <c r="G9" t="s">
-        <v>60</v>
+        <v>54</v>
+      </c>
+      <c r="G9" s="2">
+        <v>43103</v>
       </c>
       <c r="H9">
         <v>187756</v>
@@ -1277,27 +1314,27 @@
         <v>56.76</v>
       </c>
     </row>
-    <row r="10" spans="1:26">
+    <row r="10" spans="1:27">
       <c r="A10">
         <v>98</v>
       </c>
       <c r="B10" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C10" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D10">
         <v>2025</v>
       </c>
       <c r="E10" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="F10" t="s">
-        <v>53</v>
-      </c>
-      <c r="G10">
-        <v>44866</v>
+        <v>54</v>
+      </c>
+      <c r="G10" s="2">
+        <v>44572</v>
       </c>
       <c r="H10">
         <v>177694</v>
@@ -1357,27 +1394,27 @@
         <v>39.72</v>
       </c>
     </row>
-    <row r="11" spans="1:26">
+    <row r="11" spans="1:27">
       <c r="A11">
         <v>99</v>
       </c>
       <c r="B11" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C11" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D11">
         <v>2025</v>
       </c>
       <c r="E11" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F11" t="s">
-        <v>53</v>
-      </c>
-      <c r="G11">
-        <v>44866</v>
+        <v>54</v>
+      </c>
+      <c r="G11" s="2">
+        <v>44572</v>
       </c>
       <c r="H11">
         <v>140310</v>
@@ -1437,27 +1474,27 @@
         <v>43.31</v>
       </c>
     </row>
-    <row r="12" spans="1:26">
+    <row r="12" spans="1:27">
       <c r="A12">
         <v>100</v>
       </c>
       <c r="B12" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C12" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D12">
         <v>2025</v>
       </c>
       <c r="E12" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="F12" t="s">
-        <v>53</v>
-      </c>
-      <c r="G12">
-        <v>45230</v>
+        <v>54</v>
+      </c>
+      <c r="G12" t="s">
+        <v>65</v>
       </c>
       <c r="H12">
         <v>91432</v>
@@ -1517,27 +1554,27 @@
         <v>27.29</v>
       </c>
     </row>
-    <row r="13" spans="1:26">
+    <row r="13" spans="1:27">
       <c r="A13">
         <v>101</v>
       </c>
       <c r="B13" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C13" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D13">
         <v>2025</v>
       </c>
       <c r="E13" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="F13" t="s">
-        <v>53</v>
-      </c>
-      <c r="G13">
-        <v>45230</v>
+        <v>54</v>
+      </c>
+      <c r="G13" t="s">
+        <v>65</v>
       </c>
       <c r="H13">
         <v>79669</v>
@@ -1597,27 +1634,27 @@
         <v>20.22</v>
       </c>
     </row>
-    <row r="14" spans="1:26">
+    <row r="14" spans="1:27">
       <c r="A14">
         <v>102</v>
       </c>
       <c r="B14" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C14" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D14">
         <v>2025</v>
       </c>
       <c r="E14" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="F14" t="s">
-        <v>53</v>
-      </c>
-      <c r="G14">
-        <v>43825</v>
+        <v>54</v>
+      </c>
+      <c r="G14" t="s">
+        <v>66</v>
       </c>
       <c r="H14">
         <v>57968</v>
@@ -1677,27 +1714,27 @@
         <v>59.33</v>
       </c>
     </row>
-    <row r="15" spans="1:26">
+    <row r="15" spans="1:27">
       <c r="A15">
         <v>103</v>
       </c>
       <c r="B15" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C15" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D15">
         <v>2025</v>
       </c>
       <c r="E15" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="F15" t="s">
-        <v>54</v>
-      </c>
-      <c r="G15">
-        <v>44712</v>
+        <v>55</v>
+      </c>
+      <c r="G15" t="s">
+        <v>67</v>
       </c>
       <c r="H15">
         <v>70197</v>
@@ -1757,27 +1794,27 @@
         <v>-29.56</v>
       </c>
     </row>
-    <row r="16" spans="1:26">
+    <row r="16" spans="1:27">
       <c r="A16">
         <v>104</v>
       </c>
       <c r="B16" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C16" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D16">
         <v>2025</v>
       </c>
       <c r="E16" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="F16" t="s">
-        <v>55</v>
-      </c>
-      <c r="G16">
-        <v>43554</v>
+        <v>56</v>
+      </c>
+      <c r="G16" t="s">
+        <v>68</v>
       </c>
       <c r="H16">
         <v>91359</v>
@@ -1842,22 +1879,22 @@
         <v>105</v>
       </c>
       <c r="B17" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C17" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D17">
         <v>2025</v>
       </c>
       <c r="E17" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="F17" t="s">
-        <v>55</v>
-      </c>
-      <c r="G17">
-        <v>43663</v>
+        <v>56</v>
+      </c>
+      <c r="G17" t="s">
+        <v>69</v>
       </c>
       <c r="H17">
         <v>69570</v>
@@ -1922,22 +1959,22 @@
         <v>106</v>
       </c>
       <c r="B18" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C18" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D18">
         <v>2025</v>
       </c>
       <c r="E18" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="F18" t="s">
-        <v>56</v>
-      </c>
-      <c r="G18" t="s">
-        <v>60</v>
+        <v>57</v>
+      </c>
+      <c r="G18" s="2">
+        <v>45352</v>
       </c>
       <c r="H18">
         <v>97315</v>
@@ -2002,22 +2039,22 @@
         <v>107</v>
       </c>
       <c r="B19" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C19" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D19">
         <v>2025</v>
       </c>
       <c r="E19" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="F19" t="s">
-        <v>56</v>
-      </c>
-      <c r="G19" t="s">
-        <v>60</v>
+        <v>57</v>
+      </c>
+      <c r="G19" s="2">
+        <v>45352</v>
       </c>
       <c r="H19">
         <v>94815</v>
@@ -2082,22 +2119,22 @@
         <v>108</v>
       </c>
       <c r="B20" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C20" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D20">
         <v>2025</v>
       </c>
       <c r="E20" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="F20" t="s">
-        <v>56</v>
-      </c>
-      <c r="G20" t="s">
-        <v>60</v>
+        <v>57</v>
+      </c>
+      <c r="G20" s="2">
+        <v>45352</v>
       </c>
       <c r="H20">
         <v>84418</v>
@@ -2162,22 +2199,22 @@
         <v>109</v>
       </c>
       <c r="B21" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C21" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D21">
         <v>2025</v>
       </c>
       <c r="E21" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="F21" t="s">
-        <v>57</v>
-      </c>
-      <c r="G21">
-        <v>45363</v>
+        <v>58</v>
+      </c>
+      <c r="G21" s="2">
+        <v>45629</v>
       </c>
       <c r="H21">
         <v>33315</v>
@@ -2242,22 +2279,22 @@
         <v>110</v>
       </c>
       <c r="B22" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C22" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D22">
         <v>2025</v>
       </c>
       <c r="E22" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="F22" t="s">
-        <v>57</v>
-      </c>
-      <c r="G22">
-        <v>45363</v>
+        <v>58</v>
+      </c>
+      <c r="G22" s="2">
+        <v>45629</v>
       </c>
       <c r="H22">
         <v>26322</v>
@@ -2322,22 +2359,22 @@
         <v>111</v>
       </c>
       <c r="B23" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C23" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D23">
         <v>2025</v>
       </c>
       <c r="E23" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="F23" t="s">
-        <v>58</v>
-      </c>
-      <c r="G23">
-        <v>45365</v>
+        <v>59</v>
+      </c>
+      <c r="G23" t="s">
+        <v>70</v>
       </c>
       <c r="H23">
         <v>42375</v>
@@ -2402,22 +2439,22 @@
         <v>112</v>
       </c>
       <c r="B24" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C24" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D24">
         <v>2025</v>
       </c>
       <c r="E24" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="F24" t="s">
-        <v>59</v>
-      </c>
-      <c r="G24">
-        <v>45392</v>
+        <v>60</v>
+      </c>
+      <c r="G24" s="2">
+        <v>45569</v>
       </c>
       <c r="H24">
         <v>54066</v>
@@ -2482,22 +2519,22 @@
         <v>113</v>
       </c>
       <c r="B25" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C25" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D25">
         <v>2025</v>
       </c>
       <c r="E25" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="F25" t="s">
-        <v>59</v>
-      </c>
-      <c r="G25">
-        <v>45392</v>
+        <v>60</v>
+      </c>
+      <c r="G25" s="2">
+        <v>45569</v>
       </c>
       <c r="H25">
         <v>67046</v>
